--- a/data/trans_orig/P23_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158961</t>
+          <t>156271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>201892</t>
+          <t>199676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>137242</t>
+          <t>135897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179899</t>
+          <t>175500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306823</t>
+          <t>306871</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>365086</t>
+          <t>364666</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291130</t>
+          <t>293346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334061</t>
+          <t>336751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287590</t>
+          <t>291989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>330247</t>
+          <t>331592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595425</t>
+          <t>595845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>653688</t>
+          <t>653640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>337101</t>
+          <t>335011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>391362</t>
+          <t>391410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196209</t>
+          <t>195432</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>242893</t>
+          <t>240268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>545432</t>
+          <t>544038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>621129</t>
+          <t>621101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344127</t>
+          <t>344079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398388</t>
+          <t>400478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>382601</t>
+          <t>385226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>429285</t>
+          <t>430062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739853</t>
+          <t>739881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>815550</t>
+          <t>816944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>308012</t>
+          <t>307474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>359030</t>
+          <t>357688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231565</t>
+          <t>229990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>282635</t>
+          <t>286067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>553652</t>
+          <t>553476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>624690</t>
+          <t>623502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>279638</t>
+          <t>280980</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330656</t>
+          <t>331194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>407109</t>
+          <t>403677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458179</t>
+          <t>459754</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>703722</t>
+          <t>704910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>774760</t>
+          <t>774936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205801</t>
+          <t>204989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>252297</t>
+          <t>253173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121958</t>
+          <t>121383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162220</t>
+          <t>162251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339881</t>
+          <t>340376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404180</t>
+          <t>399970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>266850</t>
+          <t>265974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313346</t>
+          <t>314158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353422</t>
+          <t>353391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>393684</t>
+          <t>394259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630609</t>
+          <t>634819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694908</t>
+          <t>694413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109441</t>
+          <t>112451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147496</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35857</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>62900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151494</t>
+          <t>152635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200470</t>
+          <t>199747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>239214</t>
+          <t>239429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>277269</t>
+          <t>274259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342532</t>
+          <t>341086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368129</t>
+          <t>368411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>590226</t>
+          <t>590949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>639202</t>
+          <t>638061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66669</t>
+          <t>66732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47755</t>
+          <t>48053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75126</t>
+          <t>76143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225914</t>
+          <t>225851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250645</t>
+          <t>251637</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>328811</t>
+          <t>329583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>340101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560391</t>
+          <t>559374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>587762</t>
+          <t>587464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177032</t>
+          <t>177406</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194866</t>
+          <t>194473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>323207</t>
+          <t>322301</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332778</t>
+          <t>332793</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>505265</t>
+          <t>505920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>525423</t>
+          <t>525692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1244842</t>
+          <t>1252736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1361477</t>
+          <t>1365380</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>785050</t>
+          <t>781070</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>885840</t>
+          <t>876985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2055957</t>
+          <t>2058038</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2216426</t>
+          <t>2217789</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1914024</t>
+          <t>1910121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2030659</t>
+          <t>2022765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2493357</t>
+          <t>2502212</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2594147</t>
+          <t>2598127</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4438272</t>
+          <t>4436909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4598741</t>
+          <t>4596660</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117867</t>
+          <t>119696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158445</t>
+          <t>158295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123929</t>
+          <t>121563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164203</t>
+          <t>159722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>250155</t>
+          <t>252132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>307097</t>
+          <t>307256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295701</t>
+          <t>295851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336279</t>
+          <t>334450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265031</t>
+          <t>269512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305305</t>
+          <t>307671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>576283</t>
+          <t>576124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>633225</t>
+          <t>631248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,46%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>276674</t>
+          <t>273260</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>327411</t>
+          <t>328952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223768</t>
+          <t>220919</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>268793</t>
+          <t>269779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>511346</t>
+          <t>509660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>584180</t>
+          <t>582552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359676</t>
+          <t>358135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410413</t>
+          <t>413827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341462</t>
+          <t>340476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>386487</t>
+          <t>389336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713162</t>
+          <t>714790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>785996</t>
+          <t>787682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,72%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286871</t>
+          <t>286354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>336858</t>
+          <t>338159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>218414</t>
+          <t>215494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269257</t>
+          <t>269927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>519275</t>
+          <t>518472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>592873</t>
+          <t>593966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343975</t>
+          <t>342674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>393962</t>
+          <t>394479</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>440607</t>
+          <t>439937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>491450</t>
+          <t>494370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>797824</t>
+          <t>796731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>871422</t>
+          <t>872225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252629</t>
+          <t>251918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>308003</t>
+          <t>305007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215624</t>
+          <t>215303</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266833</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>481340</t>
+          <t>480821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>556150</t>
+          <t>552838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306614</t>
+          <t>309610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361988</t>
+          <t>362699</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349366</t>
+          <t>349069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>400575</t>
+          <t>400896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>674666</t>
+          <t>677978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749476</t>
+          <t>749995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>135866</t>
+          <t>134040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177455</t>
+          <t>175997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52747</t>
+          <t>53366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>197585</t>
+          <t>194661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>252713</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251974</t>
+          <t>253432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293563</t>
+          <t>295389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>362329</t>
+          <t>362740</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>395053</t>
+          <t>394434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>626163</t>
+          <t>624516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>679644</t>
+          <t>682568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37554</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66987</t>
+          <t>68496</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29630</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54166</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88616</t>
+          <t>90789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242799</t>
+          <t>241290</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272232</t>
+          <t>270573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>324366</t>
+          <t>323524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342483</t>
+          <t>342679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>575166</t>
+          <t>572993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609616</t>
+          <t>609772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211113</t>
+          <t>211781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232221</t>
+          <t>232156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377743</t>
+          <t>376090</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>593358</t>
+          <t>594390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>617795</t>
+          <t>617356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1206177</t>
+          <t>1203028</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1328041</t>
+          <t>1319774</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>902400</t>
+          <t>905512</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1013655</t>
+          <t>1012153</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2136501</t>
+          <t>2142650</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2303716</t>
+          <t>2302854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2097708</t>
+          <t>2105975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2219572</t>
+          <t>2222721</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2542672</t>
+          <t>2544174</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2653927</t>
+          <t>2650815</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4678360</t>
+          <t>4679222</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4845575</t>
+          <t>4839426</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123790</t>
+          <t>124021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162101</t>
+          <t>162345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89523</t>
+          <t>89449</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122649</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>224044</t>
+          <t>221671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277723</t>
+          <t>275568</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257362</t>
+          <t>257118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295673</t>
+          <t>295442</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273106</t>
+          <t>271736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306232</t>
+          <t>306306</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537495</t>
+          <t>539650</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591174</t>
+          <t>593547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236312</t>
+          <t>238045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285444</t>
+          <t>288415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189244</t>
+          <t>188908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233821</t>
+          <t>234719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>440642</t>
+          <t>439919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>507331</t>
+          <t>505781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,83%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>305052</t>
+          <t>302081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354184</t>
+          <t>352451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329723</t>
+          <t>328825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374300</t>
+          <t>374636</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646709</t>
+          <t>648259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713398</t>
+          <t>714121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,88%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>241681</t>
+          <t>240988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>293841</t>
+          <t>291463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>198589</t>
+          <t>197920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244723</t>
+          <t>245906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>452492</t>
+          <t>452222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>526036</t>
+          <t>524396</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>374184</t>
+          <t>376562</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426344</t>
+          <t>427037</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>415736</t>
+          <t>414553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461870</t>
+          <t>462539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>802447</t>
+          <t>804087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>875991</t>
+          <t>876261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253205</t>
+          <t>250782</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>304927</t>
+          <t>304513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205606</t>
+          <t>205357</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>256156</t>
+          <t>254014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>474020</t>
+          <t>472457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550508</t>
+          <t>544996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341121</t>
+          <t>341535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>392843</t>
+          <t>395266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390805</t>
+          <t>392947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441355</t>
+          <t>441604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742501</t>
+          <t>748013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>818989</t>
+          <t>820552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126011</t>
+          <t>125451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169646</t>
+          <t>168060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95907</t>
+          <t>95243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136149</t>
+          <t>133819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232382</t>
+          <t>233352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292545</t>
+          <t>289122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,69%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308272</t>
+          <t>309858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>351907</t>
+          <t>352467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>359591</t>
+          <t>361921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399833</t>
+          <t>400497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681113</t>
+          <t>684536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>741276</t>
+          <t>740306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45592</t>
+          <t>43907</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72535</t>
+          <t>74340</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20451</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71407</t>
+          <t>72234</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>110461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261795</t>
+          <t>259990</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288738</t>
+          <t>290423</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334355</t>
+          <t>336188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>357311</t>
+          <t>358169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>605738</t>
+          <t>601631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>640685</t>
+          <t>639858</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16386</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33050</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43701</t>
+          <t>44679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>223083</t>
+          <t>222948</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239747</t>
+          <t>239091</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>382643</t>
+          <t>382367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396114</t>
+          <t>396116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>611316</t>
+          <t>610338</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>633880</t>
+          <t>632711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1119083</t>
+          <t>1118666</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1234664</t>
+          <t>1233119</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>870508</t>
+          <t>869521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>975209</t>
+          <t>974405</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2015020</t>
+          <t>2015671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2174439</t>
+          <t>2174376</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2157750</t>
+          <t>2159295</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2273331</t>
+          <t>2273748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2563894</t>
+          <t>2564698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2668595</t>
+          <t>2669582</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4757078</t>
+          <t>4757141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4916497</t>
+          <t>4915846</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65669</t>
+          <t>66135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124562</t>
+          <t>123357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80968</t>
+          <t>82045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123500</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191385</t>
+          <t>195586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275425</t>
+          <t>276630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334318</t>
+          <t>333852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229670</t>
+          <t>228593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265447</t>
+          <t>265301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519240</t>
+          <t>515039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587125</t>
+          <t>590224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121781</t>
+          <t>125692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172866</t>
+          <t>173285</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72213</t>
+          <t>69341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142867</t>
+          <t>142967</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201184</t>
+          <t>202145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>300261</t>
+          <t>301354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250681</t>
+          <t>250262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>301766</t>
+          <t>297855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368637</t>
+          <t>368537</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>439291</t>
+          <t>442163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>634790</t>
+          <t>633697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733867</t>
+          <t>732906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126658</t>
+          <t>129432</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169151</t>
+          <t>171049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119834</t>
+          <t>120260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153475</t>
+          <t>154092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>258470</t>
+          <t>257721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311262</t>
+          <t>311825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>367023</t>
+          <t>365125</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>409516</t>
+          <t>406742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>388993</t>
+          <t>388376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>422634</t>
+          <t>422208</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>767379</t>
+          <t>766816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820171</t>
+          <t>820920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79932</t>
+          <t>84197</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>266663</t>
+          <t>269133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135644</t>
+          <t>135634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181768</t>
+          <t>183129</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193424</t>
+          <t>204890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>419401</t>
+          <t>422474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>620120</t>
+          <t>617650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>806851</t>
+          <t>802586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>529769</t>
+          <t>528408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>575893</t>
+          <t>575903</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1178919</t>
+          <t>1175846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1404896</t>
+          <t>1393430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153041</t>
+          <t>153573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194118</t>
+          <t>195400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107073</t>
+          <t>107426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135744</t>
+          <t>137912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273028</t>
+          <t>271396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323486</t>
+          <t>321799</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366086</t>
+          <t>364804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>407163</t>
+          <t>406631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>412161</t>
+          <t>409993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440832</t>
+          <t>440479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>784623</t>
+          <t>786310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>835081</t>
+          <t>836713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57240</t>
+          <t>56929</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82457</t>
+          <t>81252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78799</t>
+          <t>79770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66530</t>
+          <t>61668</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154890</t>
+          <t>154196</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285708</t>
+          <t>286913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>310925</t>
+          <t>311236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>529569</t>
+          <t>528598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588594</t>
+          <t>587522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>821643</t>
+          <t>822337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>910003</t>
+          <t>914865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>13438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27060</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34277</t>
+          <t>34325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255699</t>
+          <t>255830</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270316</t>
+          <t>269321</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>415479</t>
+          <t>414874</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>422541</t>
+          <t>422508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674313</t>
+          <t>674265</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>689813</t>
+          <t>690014</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>665502</t>
+          <t>659122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>926490</t>
+          <t>919495</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>525297</t>
+          <t>541235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>713537</t>
+          <t>718797</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1287875</t>
+          <t>1274431</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1605712</t>
+          <t>1605487</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2531130</t>
+          <t>2538125</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2792118</t>
+          <t>2798498</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2944714</t>
+          <t>2939454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3132954</t>
+          <t>3117016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5510159</t>
+          <t>5510384</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5827996</t>
+          <t>5841440</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156271</t>
+          <t>157065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>199676</t>
+          <t>201344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135897</t>
+          <t>136996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>175500</t>
+          <t>175946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306871</t>
+          <t>303853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>364666</t>
+          <t>365447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293346</t>
+          <t>291678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336751</t>
+          <t>335957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291989</t>
+          <t>291543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>331592</t>
+          <t>330493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>595845</t>
+          <t>595064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>653640</t>
+          <t>656658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>335011</t>
+          <t>333473</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>391410</t>
+          <t>388370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195432</t>
+          <t>193774</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240268</t>
+          <t>243588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>544038</t>
+          <t>542433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>621101</t>
+          <t>617650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344079</t>
+          <t>347119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400478</t>
+          <t>402016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>385226</t>
+          <t>381906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>430062</t>
+          <t>431720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739881</t>
+          <t>743332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>816944</t>
+          <t>818549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>307474</t>
+          <t>306650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>357688</t>
+          <t>362088</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229990</t>
+          <t>231056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>286067</t>
+          <t>281802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>553476</t>
+          <t>551574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>623502</t>
+          <t>624465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280980</t>
+          <t>276580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>331194</t>
+          <t>332018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>403677</t>
+          <t>407942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>459754</t>
+          <t>458688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>704910</t>
+          <t>703947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>774936</t>
+          <t>776838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204989</t>
+          <t>205647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>253173</t>
+          <t>251252</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>121383</t>
+          <t>122454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162251</t>
+          <t>163953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340376</t>
+          <t>339442</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399970</t>
+          <t>401310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>265974</t>
+          <t>267895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>314158</t>
+          <t>313500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>353391</t>
+          <t>351689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>394259</t>
+          <t>393188</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634819</t>
+          <t>633479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694413</t>
+          <t>695347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>112451</t>
+          <t>109440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147281</t>
+          <t>145811</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>33863</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62900</t>
+          <t>61300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152635</t>
+          <t>153555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>199747</t>
+          <t>199264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>239429</t>
+          <t>240899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274259</t>
+          <t>277270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>341086</t>
+          <t>342686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>368411</t>
+          <t>370123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>590949</t>
+          <t>591432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>638061</t>
+          <t>637141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66732</t>
+          <t>65864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48053</t>
+          <t>47497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76143</t>
+          <t>76448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225851</t>
+          <t>226719</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251637</t>
+          <t>251131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>329583</t>
+          <t>329798</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340101</t>
+          <t>340115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559374</t>
+          <t>559069</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>587464</t>
+          <t>588020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32477</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>39712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177406</t>
+          <t>177927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>194473</t>
+          <t>195305</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>322301</t>
+          <t>322697</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332793</t>
+          <t>332779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>505920</t>
+          <t>504079</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>525692</t>
+          <t>525052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1252736</t>
+          <t>1249910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1365380</t>
+          <t>1361442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>781070</t>
+          <t>782094</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>876985</t>
+          <t>883362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2058038</t>
+          <t>2061715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2217789</t>
+          <t>2208510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1910121</t>
+          <t>1914059</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2022765</t>
+          <t>2025591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2502212</t>
+          <t>2495835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2598127</t>
+          <t>2597103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4436909</t>
+          <t>4446188</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4596660</t>
+          <t>4592983</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119696</t>
+          <t>116265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158295</t>
+          <t>157058</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121563</t>
+          <t>121891</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159722</t>
+          <t>160597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252132</t>
+          <t>252790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>307256</t>
+          <t>308436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295851</t>
+          <t>297088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334450</t>
+          <t>337881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269512</t>
+          <t>268637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307671</t>
+          <t>307343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>576124</t>
+          <t>574944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631248</t>
+          <t>630590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>273260</t>
+          <t>275758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>328952</t>
+          <t>328139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220919</t>
+          <t>221066</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>269779</t>
+          <t>270339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>509660</t>
+          <t>508964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>582552</t>
+          <t>579886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358135</t>
+          <t>358948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413827</t>
+          <t>411329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340476</t>
+          <t>339916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>389336</t>
+          <t>389189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>714790</t>
+          <t>717456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>787682</t>
+          <t>788378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>286354</t>
+          <t>285588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>338159</t>
+          <t>337111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>215494</t>
+          <t>215636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>269927</t>
+          <t>268170</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>518472</t>
+          <t>521181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>593966</t>
+          <t>593353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>342674</t>
+          <t>343722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>394479</t>
+          <t>395245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>439937</t>
+          <t>441694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494370</t>
+          <t>494228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>796731</t>
+          <t>797344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>872225</t>
+          <t>869516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251918</t>
+          <t>253112</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>305007</t>
+          <t>304378</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215303</t>
+          <t>212273</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>267130</t>
+          <t>263087</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>480821</t>
+          <t>480637</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>552838</t>
+          <t>552469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>309610</t>
+          <t>310239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>362699</t>
+          <t>361505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349069</t>
+          <t>353112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>400896</t>
+          <t>403926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>677978</t>
+          <t>678347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749995</t>
+          <t>750179</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>134040</t>
+          <t>135962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175997</t>
+          <t>178277</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53366</t>
+          <t>53185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85060</t>
+          <t>85499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194661</t>
+          <t>195703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>252713</t>
+          <t>251654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>253432</t>
+          <t>251152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>295389</t>
+          <t>293467</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>362740</t>
+          <t>362301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>394434</t>
+          <t>394615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>624516</t>
+          <t>625575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682568</t>
+          <t>681526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>38541</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68496</t>
+          <t>66479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30472</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>55994</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>90789</t>
+          <t>89249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>241290</t>
+          <t>243307</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270573</t>
+          <t>271245</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>323524</t>
+          <t>323395</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>342679</t>
+          <t>342640</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>572993</t>
+          <t>574533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609772</t>
+          <t>607788</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>18278</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21474</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>45497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>211781</t>
+          <t>211244</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232156</t>
+          <t>231573</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>376090</t>
+          <t>377073</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387970</t>
+          <t>387973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>594390</t>
+          <t>593333</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>617356</t>
+          <t>618284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1203028</t>
+          <t>1207570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1319774</t>
+          <t>1324861</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>905512</t>
+          <t>901501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1012153</t>
+          <t>1014393</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2142650</t>
+          <t>2140869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2302854</t>
+          <t>2304193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2105975</t>
+          <t>2100888</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2222721</t>
+          <t>2218179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2544174</t>
+          <t>2541934</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2650815</t>
+          <t>2654826</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4679222</t>
+          <t>4677883</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4839426</t>
+          <t>4841207</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124021</t>
+          <t>123939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162345</t>
+          <t>161891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89449</t>
+          <t>88657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124019</t>
+          <t>123711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221671</t>
+          <t>222468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275568</t>
+          <t>276471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257118</t>
+          <t>257572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295442</t>
+          <t>295524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271736</t>
+          <t>272044</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306306</t>
+          <t>307098</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539650</t>
+          <t>538747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593547</t>
+          <t>592750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238045</t>
+          <t>234816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288415</t>
+          <t>284272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188908</t>
+          <t>191132</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234719</t>
+          <t>237623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>439919</t>
+          <t>440089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>505781</t>
+          <t>505162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>302081</t>
+          <t>306224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352451</t>
+          <t>355680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>328825</t>
+          <t>325921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374636</t>
+          <t>372412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648259</t>
+          <t>648878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>714121</t>
+          <t>713951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240988</t>
+          <t>242329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>291463</t>
+          <t>293195</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>197920</t>
+          <t>197257</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>245906</t>
+          <t>245724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>452222</t>
+          <t>450557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>524396</t>
+          <t>523866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>376562</t>
+          <t>374830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427037</t>
+          <t>425696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>414553</t>
+          <t>414735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>462539</t>
+          <t>463202</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>804087</t>
+          <t>804617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>876261</t>
+          <t>877926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>250782</t>
+          <t>249750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>304513</t>
+          <t>305086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205357</t>
+          <t>205186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254014</t>
+          <t>254108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>472457</t>
+          <t>471895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>544996</t>
+          <t>544464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341535</t>
+          <t>340962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>395266</t>
+          <t>396298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>392947</t>
+          <t>392853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441604</t>
+          <t>441775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>748013</t>
+          <t>748545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>820552</t>
+          <t>821114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125451</t>
+          <t>125185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168060</t>
+          <t>168245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95243</t>
+          <t>94486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133819</t>
+          <t>133653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233352</t>
+          <t>231726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289122</t>
+          <t>291316</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>309858</t>
+          <t>309673</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352467</t>
+          <t>352733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361921</t>
+          <t>362087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>400497</t>
+          <t>401254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>684536</t>
+          <t>682342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>740306</t>
+          <t>741932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74340</t>
+          <t>72489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>41477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72234</t>
+          <t>72358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110461</t>
+          <t>110091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259990</t>
+          <t>261841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290423</t>
+          <t>290127</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336188</t>
+          <t>336285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358169</t>
+          <t>356943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>601631</t>
+          <t>602001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>639858</t>
+          <t>639734</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,84%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33185</t>
+          <t>33414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44679</t>
+          <t>45009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>222948</t>
+          <t>222719</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239091</t>
+          <t>239320</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>382367</t>
+          <t>381727</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396116</t>
+          <t>396160</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>610338</t>
+          <t>610008</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>632711</t>
+          <t>632574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1118666</t>
+          <t>1127117</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1233119</t>
+          <t>1237940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>869521</t>
+          <t>869748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>974405</t>
+          <t>982473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2015671</t>
+          <t>2019716</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2174376</t>
+          <t>2177719</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2159295</t>
+          <t>2154474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2273748</t>
+          <t>2265297</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2564698</t>
+          <t>2556630</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2669582</t>
+          <t>2669355</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4757141</t>
+          <t>4753798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4915846</t>
+          <t>4911801</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>91625</t>
+          <t>93153</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66135</t>
+          <t>66707</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123357</t>
+          <t>123126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>68600</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>50465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82045</t>
+          <t>93511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,22 +9735,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>153298</t>
+          <t>161754</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120401</t>
+          <t>130110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195586</t>
+          <t>197039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308362</t>
+          <t>314640</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276630</t>
+          <t>284667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>333852</t>
+          <t>341086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>248964</t>
+          <t>291448</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228593</t>
+          <t>266537</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265301</t>
+          <t>309583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>557327</t>
+          <t>606088</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515039</t>
+          <t>570803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>590224</t>
+          <t>637732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310638</t>
+          <t>360048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>710625</t>
+          <t>767842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>147029</t>
+          <t>161617</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125692</t>
+          <t>139470</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173285</t>
+          <t>191350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>114930</t>
+          <t>122038</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69341</t>
+          <t>101318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142967</t>
+          <t>143451</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>261959</t>
+          <t>283654</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>202145</t>
+          <t>250915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>301354</t>
+          <t>315727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>276518</t>
+          <t>315273</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250262</t>
+          <t>285540</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>297855</t>
+          <t>337420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>396574</t>
+          <t>379045</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>368537</t>
+          <t>357632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442163</t>
+          <t>399765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>673092</t>
+          <t>694319</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633697</t>
+          <t>662246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732906</t>
+          <t>727058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>149647</t>
+          <t>168348</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>129432</t>
+          <t>145389</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171049</t>
+          <t>191965</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135854</t>
+          <t>146458</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120260</t>
+          <t>128040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154092</t>
+          <t>163810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>285502</t>
+          <t>314806</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257721</t>
+          <t>285302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311825</t>
+          <t>344754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>386527</t>
+          <t>451311</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365125</t>
+          <t>427694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>406742</t>
+          <t>474270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>406614</t>
+          <t>475681</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>388376</t>
+          <t>458329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>422208</t>
+          <t>494099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>793139</t>
+          <t>926992</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>766816</t>
+          <t>897044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>820920</t>
+          <t>956496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>77,03%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078641</t>
+          <t>1241798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>184758</t>
+          <t>195321</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84197</t>
+          <t>170871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269133</t>
+          <t>220042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>162735</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>135634</t>
+          <t>158294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>183129</t>
+          <t>193583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>347493</t>
+          <t>369762</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204890</t>
+          <t>339022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>422474</t>
+          <t>399842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>702025</t>
+          <t>504155</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617650</t>
+          <t>479434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802586</t>
+          <t>528605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>548802</t>
+          <t>561037</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528408</t>
+          <t>541895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>575903</t>
+          <t>577184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1250827</t>
+          <t>1065192</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1175846</t>
+          <t>1035112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1393430</t>
+          <t>1095932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886783</t>
+          <t>699476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711537</t>
+          <t>735478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1598320</t>
+          <t>1434954</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>173978</t>
+          <t>188232</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153573</t>
+          <t>167490</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195400</t>
+          <t>213175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>121680</t>
+          <t>134336</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107426</t>
+          <t>120569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137912</t>
+          <t>150700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>295657</t>
+          <t>322567</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>271396</t>
+          <t>296604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321799</t>
+          <t>354531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>386226</t>
+          <t>420033</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364804</t>
+          <t>395090</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>406631</t>
+          <t>440775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>426225</t>
+          <t>474519</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>409993</t>
+          <t>458155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>440479</t>
+          <t>488286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>812452</t>
+          <t>894553</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>786310</t>
+          <t>862589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>836713</t>
+          <t>920516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108109</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>68443</t>
+          <t>74883</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56929</t>
+          <t>62556</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81252</t>
+          <t>90127</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>54563</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>45229</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79770</t>
+          <t>65897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>117223</t>
+          <t>129446</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61668</t>
+          <t>114666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154196</t>
+          <t>147052</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>299722</t>
+          <t>332197</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286913</t>
+          <t>316953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>311236</t>
+          <t>344524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>559588</t>
+          <t>384603</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>528598</t>
+          <t>373269</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>587522</t>
+          <t>393937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>859310</t>
+          <t>716800</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>822337</t>
+          <t>699194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>914865</t>
+          <t>731580</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,22 +11758,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>36843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>263728</t>
+          <t>290003</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255830</t>
+          <t>281948</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>269321</t>
+          <t>296787</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,27 +11871,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>419537</t>
+          <t>457831</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>414874</t>
+          <t>453082</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>422508</t>
+          <t>460990</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>683265</t>
+          <t>747835</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674265</t>
+          <t>737964</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>690014</t>
+          <t>755303</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>834510</t>
+          <t>901748</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>659122</t>
+          <t>847849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>919495</t>
+          <t>964672</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>651946</t>
+          <t>707214</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>541235</t>
+          <t>666059</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>718797</t>
+          <t>753555</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1486457</t>
+          <t>1608962</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1274431</t>
+          <t>1528923</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1605487</t>
+          <t>1683254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2623110</t>
+          <t>2627613</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2538125</t>
+          <t>2564689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2798498</t>
+          <t>2681512</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3006305</t>
+          <t>3024166</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2939454</t>
+          <t>2977825</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3117016</t>
+          <t>3065321</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5629414</t>
+          <t>5651778</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5510384</t>
+          <t>5577486</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5841440</t>
+          <t>5731817</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
